--- a/analyses/Cys/Table1.xlsx
+++ b/analyses/Cys/Table1.xlsx
@@ -378,7 +378,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>1.31348195922648</v>
+        <v>1.485363571746019</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -393,7 +393,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.9050119634465873</v>
+        <v>0.8454460692778479</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -408,7 +408,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.5608482482674205</v>
+        <v>0.5407013982422602</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -423,7 +423,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.3868716678174129</v>
+        <v>0.3646917978210163</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -434,315 +434,315 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TP53 (Tyr 163)</t>
+          <t>FGFR3 (Ser 249)</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.2483407574776941</v>
+        <v>0.3564984068491649</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lung Squamous Cell Carcinoma (16.67%), Ovarian Cancer (14.29%), Head Neck Squamous Cell Carcinoma (11.9%)</t>
+          <t>Urothelial Cancer (79.55%), Head Neck Squamous Cell Carcinoma (9.09%), Lung Squamous Cell Carcinoma (9.09%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FGFR3 (Ser 249)</t>
+          <t>IDH1 (Arg 132)</t>
         </is>
       </c>
       <c r="B7">
-        <v>0.2164870542814349</v>
+        <v>0.3073727027554167</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Urothelial Cancer (79.55%), Head Neck Squamous Cell Carcinoma (9.09%), Lung Squamous Cell Carcinoma (9.09%)</t>
+          <t>Malignant Melanoma (22.97%), Astrocytoma (17.57%), Acute myeloid leukemia NOS (17.57%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IDH1 (Arg 132)</t>
+          <t>TP53 (Tyr 163)</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.2094073476768467</v>
+        <v>0.281391443335464</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malignant Melanoma (22.97%), Astrocytoma (17.57%), Acute myeloid leukemia NOS (17.57%)</t>
+          <t>Lung Squamous Cell Carcinoma (16.67%), Ovarian Cancer (14.29%), Head Neck Squamous Cell Carcinoma (11.9%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RARS2 (Arg 6)</t>
+          <t>KRAS (Gly 13)</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.158665426383854</v>
+        <v>0.1833315223355531</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Urothelial Cancer (35%), Breast Carcinoma (25%), Lung Adenocarcinoma (15%)</t>
+          <t>Lung Adenocarcinoma (57.14%), Endometrial Cancer (14.29%), Colorectal Adenocarcinoma (9.52%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FBXW7 (Arg 505)</t>
+          <t>TP53 (Tyr 234)</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.1512694839931205</v>
+        <v>0.1775810332538076</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Colorectal Adenocarcinoma (34.62%), Endometrial Cancer (30.77%), Malignant Melanoma (3.85%)</t>
+          <t>Lung Squamous Cell Carcinoma (21.88%), Breast Carcinoma (12.5%), Urothelial Cancer (9.38%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TP53 (Tyr 236)</t>
+          <t>FBXW7 (Arg 505)</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.1501179550770378</v>
+        <v>0.1690064778806</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Head Neck Squamous Cell Carcinoma (12%), Lung Squamous Cell Carcinoma (12%), Prostate Cancer (12%)</t>
+          <t>Colorectal Adenocarcinoma (34.62%), Endometrial Cancer (30.77%), Malignant Melanoma (3.85%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GNAS (Arg 201)</t>
+          <t>RARS2 (Arg 6)</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.1483304034488961</v>
+        <v>0.1671721738745067</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pancreatic Adenocarcinoma (35.29%), Colorectal Adenocarcinoma (17.65%), Hepatocellular Carcinoma (11.76%)</t>
+          <t>Urothelial Cancer (35%), Breast Carcinoma (25%), Lung Adenocarcinoma (15%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KRAS (Gly 13)</t>
+          <t>GNAS (Arg 201)</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.1476800481716768</v>
+        <v>0.1582466747960645</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lung Adenocarcinoma (57.14%), Endometrial Cancer (14.29%), Colorectal Adenocarcinoma (9.52%)</t>
+          <t>Pancreatic Adenocarcinoma (35.29%), Colorectal Adenocarcinoma (17.65%), Hepatocellular Carcinoma (11.76%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AR (Trp 742)</t>
+          <t>TP53 (Tyr 236)</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.1454047095234892</v>
+        <v>0.1543302841196751</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prostate Cancer (100%), Seminoma (0%), Sarcoma (0%)</t>
+          <t>Head Neck Squamous Cell Carcinoma (12%), Lung Squamous Cell Carcinoma (12%), Prostate Cancer (12%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SPOP (Phe 102)</t>
+          <t>ISX (Arg 86)</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.1454047095234892</v>
+        <v>0.1466963012017207</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Prostate Cancer (100%), Seminoma (0%), Sarcoma (0%)</t>
+          <t>Malignant Melanoma (90.48%), Head Neck Squamous Cell Carcinoma (4.76%), Endometrial Cancer (4.76%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TP53 (Tyr 234)</t>
+          <t>PPP6C (Arg 264)</t>
         </is>
       </c>
       <c r="B16">
-        <v>0.1379369157645595</v>
+        <v>0.1378487448050532</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lung Squamous Cell Carcinoma (21.88%), Breast Carcinoma (12.5%), Urothelial Cancer (9.38%)</t>
+          <t>Malignant Melanoma (94.74%), Lung Squamous Cell Carcinoma (5.26%), Seminoma (0%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TP53 (Arg 337)</t>
+          <t>SMAD4 (Arg 361)</t>
         </is>
       </c>
       <c r="B17">
-        <v>0.1355261542342431</v>
+        <v>0.1339300059997464</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Head Neck Squamous Cell Carcinoma (19.05%), Breast Carcinoma (9.52%), Prostate Cancer (9.52%)</t>
+          <t>Colorectal Adenocarcinoma (47.62%), Pancreatic Adenocarcinoma (28.57%), Gastric Adenocarcinoma (14.29%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SMAD4 (Arg 361)</t>
+          <t>TP53 (Tyr 205)</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.1337810788805538</v>
+        <v>0.133559648938556</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Colorectal Adenocarcinoma (47.62%), Pancreatic Adenocarcinoma (28.57%), Gastric Adenocarcinoma (14.29%)</t>
+          <t>Hepatocellular Carcinoma (16.67%), Lung Adenocarcinoma (16.67%), Esophageal Squamous Cell Carcinoma (12.5%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ATM (Arg 337)</t>
+          <t>TP53 (Arg 337)</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.1254630337625952</v>
+        <v>0.1267724435689987</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Colorectal Adenocarcinoma (31.58%), Malignant Melanoma (10.53%), Gastric Adenocarcinoma (10.53%)</t>
+          <t>Head Neck Squamous Cell Carcinoma (19.05%), Breast Carcinoma (9.52%), Prostate Cancer (9.52%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TP53 (Tyr 205)</t>
+          <t>ATM (Arg 337)</t>
         </is>
       </c>
       <c r="B20">
-        <v>0.1168636293599134</v>
+        <v>0.1231468935519213</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hepatocellular Carcinoma (16.67%), Lung Adenocarcinoma (16.67%), Esophageal Squamous Cell Carcinoma (12.5%)</t>
+          <t>Colorectal Adenocarcinoma (31.58%), Malignant Melanoma (10.53%), Gastric Adenocarcinoma (10.53%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ISX (Arg 86)</t>
+          <t>FGFR3 (Tyr 373)</t>
         </is>
       </c>
       <c r="B21">
-        <v>0.1073033498741208</v>
+        <v>0.1198168869431741</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malignant Melanoma (90.48%), Head Neck Squamous Cell Carcinoma (4.76%), Endometrial Cancer (4.76%)</t>
+          <t>Urothelial Cancer (86.67%), Renal Cell Carcinoma (13.33%), Seminoma (0%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PPP6C (Arg 264)</t>
+          <t>CTNNB1 (Ser 33)</t>
         </is>
       </c>
       <c r="B22">
-        <v>0.09982680832484776</v>
+        <v>0.1062268695071431</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Malignant Melanoma (94.74%), Lung Squamous Cell Carcinoma (5.26%), Seminoma (0%)</t>
+          <t>Hepatocellular Carcinoma (40%), Endometrial Cancer (30%), Medulloblastoma (13.33%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FOLH1 (Arg 281)</t>
+          <t>CTNNB1 (Ser 37)</t>
         </is>
       </c>
       <c r="B23">
-        <v>0.09695666550726156</v>
+        <v>0.1031594970223937</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Colorectal Adenocarcinoma (88.89%), Lung Adenocarcinoma (11.11%), Seminoma (0%)</t>
+          <t>Endometrial Cancer (42.86%), Hepatocellular Carcinoma (28.57%), Gastric Adenocarcinoma (9.52%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SPOP (Phe 133)</t>
+          <t>RGS7 (Arg 44)</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.09693647301565946</v>
+        <v>0.1019211457471876</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Prostate Cancer (100%), Seminoma (0%), Sarcoma (0%)</t>
+          <t>Malignant Melanoma (92.86%), Lung Squamous Cell Carcinoma (7.14%), Seminoma (0%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ARHGAP9 (Arg 66)</t>
+          <t>SVOPL (Phe 385)</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.09249784118913017</v>
+        <v>0.1014924792406945</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Colorectal Adenocarcinoma (37.5%), Breast Carcinoma (25%), Prostate Cancer (12.5%)</t>
+          <t>Lung Small Cell Carcinoma (88.89%), Pancreatic Adenocarcinoma (11.11%), Seminoma (0%)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CTNNB1 (Ser 33)</t>
+          <t>TP53 (Gly 245)</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.08159153532752861</v>
+        <v>0.1011951728417737</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hepatocellular Carcinoma (40%), Endometrial Cancer (30%), Medulloblastoma (13.33%)</t>
+          <t>Lung Squamous Cell Carcinoma (53.85%), Lung Small Cell Carcinoma (7.69%), Head Neck Squamous Cell Carcinoma (7.69%)</t>
         </is>
       </c>
     </row>
